--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-technique-imagerie.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-technique-imagerie.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3141" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3141" uniqueCount="348">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -911,6 +911,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Procedure.targetSiteCode.qualifier</t>
@@ -8675,7 +8679,7 @@
         <v>74</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>74</v>
+        <v>292</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>74</v>
@@ -8683,10 +8687,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8714,10 +8718,10 @@
         <v>198</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8788,10 +8792,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8889,17 +8893,17 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>80</v>
@@ -8917,11 +8921,11 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8972,7 +8976,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8992,10 +8996,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9020,11 +9024,11 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9075,7 +9079,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9095,10 +9099,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9196,10 +9200,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9240,7 +9244,7 @@
         <v>74</v>
       </c>
       <c r="S77" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T77" t="s" s="2">
         <v>74</v>
@@ -9299,10 +9303,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9343,7 +9347,7 @@
         <v>74</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>74</v>
@@ -9402,10 +9406,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9446,7 +9450,7 @@
         <v>74</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>74</v>
@@ -9505,10 +9509,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9608,10 +9612,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9652,7 +9656,7 @@
         <v>74</v>
       </c>
       <c r="S81" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T81" t="s" s="2">
         <v>74</v>
@@ -9711,10 +9715,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9812,10 +9816,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9913,10 +9917,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10016,10 +10020,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10119,10 +10123,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10222,10 +10226,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10253,10 +10257,10 @@
         <v>159</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10287,7 +10291,7 @@
       </c>
       <c r="Y87" s="2"/>
       <c r="Z87" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>74</v>
@@ -10305,7 +10309,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10325,10 +10329,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10428,10 +10432,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10454,7 +10458,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10507,7 +10511,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10527,10 +10531,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10553,7 +10557,7 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
@@ -10606,7 +10610,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10626,10 +10630,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10652,7 +10656,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10705,7 +10709,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10725,10 +10729,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10751,7 +10755,7 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10804,7 +10808,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10824,10 +10828,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10850,7 +10854,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10903,7 +10907,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10923,10 +10927,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10949,7 +10953,7 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11002,7 +11006,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -11022,10 +11026,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11048,7 +11052,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11101,7 +11105,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11121,10 +11125,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11147,7 +11151,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11200,7 +11204,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11220,10 +11224,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11246,7 +11250,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11299,7 +11303,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -11319,10 +11323,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11345,7 +11349,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -11398,7 +11402,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11418,10 +11422,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11444,7 +11448,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -11497,7 +11501,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
